--- a/human_resources_forms/003_recruitment_interest_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/003_recruitment_interest_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'intern'}</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Intern'}</t>
+          <t>Intern</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'entry-level'}</t>
+          <t>entry-level</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Entry-Level'}</t>
+          <t>Entry-Level</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'mid_level'}</t>
+          <t>mid_level</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Mid Level'}</t>
+          <t>Mid Level</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'senior_level'}</t>
+          <t>senior_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Senior Level'}</t>
+          <t>Senior Level</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'executive_level'}</t>
+          <t>executive_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Executive Level'}</t>
+          <t>Executive Level</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_34,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 34, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_35,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 35, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_36,_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 36, 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_37,_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 37, 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'8am-5pm'}</t>
+          <t>8am-5pm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': '8am-5pm'}</t>
+          <t>8am-5pm</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'5pm-12am'}</t>
+          <t>5pm-12am</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': '5pm-12am'}</t>
+          <t>5pm-12am</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_43,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 43, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_44,_'label':_'24/7'}</t>
+          <t>24/7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 44, 'label': '24/7'}</t>
+          <t>24/7</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_51,_'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 51, 'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_52,_'label':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 52, 'label': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_53,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 53, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_61,_'label':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 61, 'label': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_62,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 62, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_63,_'label':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 63, 'label': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_71,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 71, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_72,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 72, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_73,_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 73, 'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_81,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 81, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_82,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 82, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_83,_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 83, 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
